--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="704" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC12E55-92C9-41BD-A2EF-76C418CDBD93}"/>
+  <xr:revisionPtr revIDLastSave="705" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80F5D4BA-F2BD-4A56-9CA0-266892EFBAA1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-2023" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="60">
   <si>
     <t>Togprodukt</t>
   </si>
@@ -2852,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9A58E-6281-4D08-BF08-9517A14C48DB}">
-  <dimension ref="A1:I431"/>
+  <dimension ref="A1:I441"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2"/>
@@ -14231,6 +14231,266 @@
         <v>10.409468</v>
       </c>
       <c r="H431">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8">
+      <c r="A432" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B432" s="18">
+        <v>8</v>
+      </c>
+      <c r="C432" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D432" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E432" s="18">
+        <v>18183</v>
+      </c>
+      <c r="F432" s="18">
+        <v>17787</v>
+      </c>
+      <c r="G432" s="18">
+        <v>10.31057</v>
+      </c>
+      <c r="H432" s="18">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8">
+      <c r="A433" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B433" s="18">
+        <v>8</v>
+      </c>
+      <c r="C433" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D433" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E433" s="18">
+        <v>21778</v>
+      </c>
+      <c r="F433" s="18">
+        <v>20730</v>
+      </c>
+      <c r="G433" s="18">
+        <v>10.031658</v>
+      </c>
+      <c r="H433" s="18">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B434" s="18">
+        <v>8</v>
+      </c>
+      <c r="C434" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D434" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E434" s="18">
+        <v>22611</v>
+      </c>
+      <c r="F434" s="18">
+        <v>21257</v>
+      </c>
+      <c r="G434" s="18">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H434" s="18">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8">
+      <c r="A435" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B435" s="18">
+        <v>8</v>
+      </c>
+      <c r="C435" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D435" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E435" s="18">
+        <v>11779</v>
+      </c>
+      <c r="F435" s="18">
+        <v>11768</v>
+      </c>
+      <c r="G435" s="18">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H435" s="18">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8">
+      <c r="A436" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B436" s="18">
+        <v>8</v>
+      </c>
+      <c r="C436" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D436" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E436" s="18">
+        <v>32174</v>
+      </c>
+      <c r="F436" s="18">
+        <v>31352</v>
+      </c>
+      <c r="G436" s="18">
+        <v>10.222754</v>
+      </c>
+      <c r="H436" s="18">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8">
+      <c r="A437" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B437" s="18">
+        <v>8</v>
+      </c>
+      <c r="C437" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D437" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E437" s="18">
+        <v>18509</v>
+      </c>
+      <c r="F437" s="18">
+        <v>17981</v>
+      </c>
+      <c r="G437" s="18">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H437" s="18">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8">
+      <c r="A438" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B438" s="18">
+        <v>8</v>
+      </c>
+      <c r="C438" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D438" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E438" s="18">
+        <v>13314</v>
+      </c>
+      <c r="F438" s="18">
+        <v>13424</v>
+      </c>
+      <c r="G438" s="18">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H438" s="18">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8">
+      <c r="A439" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B439" s="18">
+        <v>8</v>
+      </c>
+      <c r="C439" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D439" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E439" s="18">
+        <v>9510</v>
+      </c>
+      <c r="F439" s="18">
+        <v>8389</v>
+      </c>
+      <c r="G439" s="18">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H439" s="18">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8">
+      <c r="A440" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B440" s="18">
+        <v>8</v>
+      </c>
+      <c r="C440" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D440" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E440" s="18">
+        <v>9512</v>
+      </c>
+      <c r="F440" s="18">
+        <v>8237</v>
+      </c>
+      <c r="G440" s="18">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H440" s="18">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8">
+      <c r="A441" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B441" s="18">
+        <v>8</v>
+      </c>
+      <c r="C441" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D441" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E441" s="18">
+        <v>60822</v>
+      </c>
+      <c r="F441" s="18">
+        <v>59548</v>
+      </c>
+      <c r="G441" s="18">
+        <v>10.409468</v>
+      </c>
+      <c r="H441" s="18">
         <v>59.271925000000003</v>
       </c>
     </row>
@@ -14293,4 +14553,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{24007f1f-a397-4c20-bfe2-4e251f78f126}" enabled="1" method="Standard" siteId="{0a8a3b9a-8dcd-4ebc-9305-f971454d49bb}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Jernbanestatistikk_2012_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="705" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80F5D4BA-F2BD-4A56-9CA0-266892EFBAA1}"/>
+  <xr:revisionPtr revIDLastSave="709" documentId="8_{97E84CCC-6234-465C-AE6C-762AAC589669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A0592C-CB0F-4B40-94D9-7BD75B611489}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DD3C63B0-74E3-455B-9E64-045F09D85D0E}"/>
   </bookViews>
   <sheets>
     <sheet name="2012-2023" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="60">
   <si>
     <t>Togprodukt</t>
   </si>
@@ -2852,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE9A58E-6281-4D08-BF08-9517A14C48DB}">
-  <dimension ref="A1:I441"/>
+  <dimension ref="A1:I451"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2"/>
@@ -14491,6 +14491,266 @@
         <v>10.409468</v>
       </c>
       <c r="H441" s="18">
+        <v>59.271925000000003</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8">
+      <c r="A442" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B442">
+        <v>9</v>
+      </c>
+      <c r="C442" t="s">
+        <v>41</v>
+      </c>
+      <c r="D442" t="s">
+        <v>6</v>
+      </c>
+      <c r="E442" s="15">
+        <v>18437.544000000002</v>
+      </c>
+      <c r="F442" s="15">
+        <v>18509.042000000005</v>
+      </c>
+      <c r="G442">
+        <v>10.31057</v>
+      </c>
+      <c r="H442">
+        <v>59.490316</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8">
+      <c r="A443" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B443">
+        <v>9</v>
+      </c>
+      <c r="C443" t="s">
+        <v>41</v>
+      </c>
+      <c r="D443" t="s">
+        <v>7</v>
+      </c>
+      <c r="E443" s="15">
+        <v>20305.087000000007</v>
+      </c>
+      <c r="F443" s="15">
+        <v>20550.490999999995</v>
+      </c>
+      <c r="G443">
+        <v>10.031658</v>
+      </c>
+      <c r="H443">
+        <v>59.050156999999999</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8">
+      <c r="A444" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B444">
+        <v>9</v>
+      </c>
+      <c r="C444" t="s">
+        <v>41</v>
+      </c>
+      <c r="D444" t="s">
+        <v>8</v>
+      </c>
+      <c r="E444" s="15">
+        <v>21814.381999999991</v>
+      </c>
+      <c r="F444" s="15">
+        <v>22187.215999999997</v>
+      </c>
+      <c r="G444">
+        <v>9.6586879999999997</v>
+      </c>
+      <c r="H444">
+        <v>59.139364</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8">
+      <c r="A445" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B445">
+        <v>9</v>
+      </c>
+      <c r="C445" t="s">
+        <v>41</v>
+      </c>
+      <c r="D445" t="s">
+        <v>9</v>
+      </c>
+      <c r="E445" s="15">
+        <v>12854.121000000001</v>
+      </c>
+      <c r="F445" s="15">
+        <v>12753.934000000001</v>
+      </c>
+      <c r="G445">
+        <v>10.204765999999999</v>
+      </c>
+      <c r="H445">
+        <v>59.585272000000003</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8">
+      <c r="A446" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B446">
+        <v>9</v>
+      </c>
+      <c r="C446" t="s">
+        <v>41</v>
+      </c>
+      <c r="D446" t="s">
+        <v>10</v>
+      </c>
+      <c r="E446" s="15">
+        <v>31014.414000000004</v>
+      </c>
+      <c r="F446" s="15">
+        <v>31120.043999999998</v>
+      </c>
+      <c r="G446">
+        <v>10.222754</v>
+      </c>
+      <c r="H446">
+        <v>59.135195000000003</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8">
+      <c r="A447" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B447">
+        <v>9</v>
+      </c>
+      <c r="C447" t="s">
+        <v>41</v>
+      </c>
+      <c r="D447" t="s">
+        <v>11</v>
+      </c>
+      <c r="E447" s="15">
+        <v>18354.352000000006</v>
+      </c>
+      <c r="F447" s="15">
+        <v>18290.120999999999</v>
+      </c>
+      <c r="G447">
+        <v>9.6035419999999991</v>
+      </c>
+      <c r="H447">
+        <v>59.219209999999997</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8">
+      <c r="A448" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B448">
+        <v>9</v>
+      </c>
+      <c r="C448" t="s">
+        <v>41</v>
+      </c>
+      <c r="D448" t="s">
+        <v>12</v>
+      </c>
+      <c r="E448" s="15">
+        <v>14026.624999999998</v>
+      </c>
+      <c r="F448" s="15">
+        <v>14212.827000000005</v>
+      </c>
+      <c r="G448">
+        <v>10.411125999999999</v>
+      </c>
+      <c r="H448">
+        <v>59.391182000000001</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8">
+      <c r="A449" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B449">
+        <v>9</v>
+      </c>
+      <c r="C449" t="s">
+        <v>41</v>
+      </c>
+      <c r="D449" t="s">
+        <v>13</v>
+      </c>
+      <c r="E449" s="15">
+        <v>8942.1860000000015</v>
+      </c>
+      <c r="F449" s="15">
+        <v>8775.9699999999939</v>
+      </c>
+      <c r="G449">
+        <v>10.300376999999999</v>
+      </c>
+      <c r="H449">
+        <v>59.221356999999998</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8">
+      <c r="A450" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B450">
+        <v>9</v>
+      </c>
+      <c r="C450" t="s">
+        <v>41</v>
+      </c>
+      <c r="D450" t="s">
+        <v>14</v>
+      </c>
+      <c r="E450" s="15">
+        <v>7877.6059999999989</v>
+      </c>
+      <c r="F450" s="15">
+        <v>8504.123999999998</v>
+      </c>
+      <c r="G450">
+        <v>10.266265000000001</v>
+      </c>
+      <c r="H450">
+        <v>59.165590000000002</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8">
+      <c r="A451" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B451">
+        <v>9</v>
+      </c>
+      <c r="C451" t="s">
+        <v>41</v>
+      </c>
+      <c r="D451" t="s">
+        <v>15</v>
+      </c>
+      <c r="E451" s="15">
+        <v>59020.616999999984</v>
+      </c>
+      <c r="F451" s="15">
+        <v>59167.83199999998</v>
+      </c>
+      <c r="G451">
+        <v>10.409468</v>
+      </c>
+      <c r="H451">
         <v>59.271925000000003</v>
       </c>
     </row>
